--- a/plantilla_tiempos.xlsx
+++ b/plantilla_tiempos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos2025\TesisModeloEmociones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABE7BA0-B693-485F-90A5-9A38B23B0858}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02111562-BF49-4E88-8DA4-5EEB02279A3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="118">
   <si>
     <t>participante</t>
   </si>
@@ -364,6 +364,21 @@
   </si>
   <si>
     <t>12:00</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>Alegria</t>
+  </si>
+  <si>
+    <t>Miedo</t>
+  </si>
+  <si>
+    <t>A2.csv</t>
+  </si>
+  <si>
+    <t>06:50</t>
   </si>
 </sst>
 </file>
@@ -373,7 +388,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -398,6 +413,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -439,7 +462,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -449,6 +472,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -788,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
@@ -799,7 +823,7 @@
     <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -819,12 +843,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -836,15 +860,15 @@
         <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>99</v>
@@ -853,73 +877,74 @@
         <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="2" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>105</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -927,19 +952,19 @@
         <v>87</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -947,19 +972,19 @@
         <v>87</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>11</v>
+        <v>60</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -967,153 +992,153 @@
         <v>87</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>15</v>
+        <v>105</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="F9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B13" t="s">
         <v>88</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B14" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>17</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B15" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F15" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
       <c r="B16" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>36</v>
+      <c r="C16" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>10</v>
@@ -1121,142 +1146,142 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>10</v>
+        <v>32</v>
+      </c>
+      <c r="F17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>10</v>
+        <v>35</v>
+      </c>
+      <c r="F18" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>7</v>
+        <v>89</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>36</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F20" t="s">
-        <v>8</v>
+        <v>41</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" t="s">
-        <v>8</v>
+        <v>43</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>53</v>
+        <v>7</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F22" t="s">
-        <v>8</v>
+        <v>46</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1267,13 +1292,13 @@
         <v>93</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F24" t="s">
         <v>8</v>
@@ -1281,79 +1306,79 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>10</v>
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>13</v>
+        <v>58</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>68</v>
+        <v>7</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>10</v>
@@ -1367,93 +1392,93 @@
         <v>95</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>71</v>
+        <v>7</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F29" t="s">
-        <v>8</v>
+        <v>64</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>7</v>
+        <v>68</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F31" t="s">
-        <v>13</v>
+        <v>70</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>7</v>
+        <v>71</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>10</v>
+        <v>73</v>
+      </c>
+      <c r="F32" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B33" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>10</v>
@@ -1461,40 +1486,92 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" t="s">
+        <v>97</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>80</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>98</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B36" t="s">
+        <v>98</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>80</v>
+      </c>
+      <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D37" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010036FD436CB14A3848AE7557D12AF2E09C" ma:contentTypeVersion="16" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="05482779405f512ea16b48451ea49083">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="8aced58e-3616-4e2c-b86f-287adbaf40b2" xmlns:ns4="676362cc-b7d6-496a-89c9-3541de701e27" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="70b59edf39fb63717ccfec3d43cf8c34" ns3:_="" ns4:_="">
     <xsd:import namespace="8aced58e-3616-4e2c-b86f-287adbaf40b2"/>
@@ -1733,6 +1810,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1742,14 +1828,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D750265-E483-4918-8CB3-B1BBB51CC830}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DF9D481-3E0E-4ADA-8B0A-BA7A6CCD5318}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1768,12 +1846,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7D750265-E483-4918-8CB3-B1BBB51CC830}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6237DEB0-A7B3-4220-B3AA-8D55AD028595}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="8aced58e-3616-4e2c-b86f-287adbaf40b2"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8aced58e-3616-4e2c-b86f-287adbaf40b2"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="676362cc-b7d6-496a-89c9-3541de701e27"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/plantilla_tiempos.xlsx
+++ b/plantilla_tiempos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repos2025\TesisModeloEmociones\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RepositorioLudolab\TesisModeloEmociones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02111562-BF49-4E88-8DA4-5EEB02279A3A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78F811E-513C-44C7-801D-3D02390BBAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="261">
   <si>
     <t>participante</t>
   </si>
@@ -183,27 +183,9 @@
     <t>01:29</t>
   </si>
   <si>
-    <t>07:29</t>
-  </si>
-  <si>
-    <t>7:30</t>
-  </si>
-  <si>
     <t>14:00</t>
   </si>
   <si>
-    <t>14:01</t>
-  </si>
-  <si>
-    <t>alegria</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>25:00</t>
-  </si>
-  <si>
     <t>16H</t>
   </si>
   <si>
@@ -219,9 +201,6 @@
     <t>03:00</t>
   </si>
   <si>
-    <t>03:35</t>
-  </si>
-  <si>
     <t>3:36</t>
   </si>
   <si>
@@ -252,21 +231,12 @@
     <t>18M</t>
   </si>
   <si>
-    <t>0:30</t>
-  </si>
-  <si>
     <t>05:21</t>
   </si>
   <si>
     <t>19M</t>
   </si>
   <si>
-    <t>02:17</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
     <t>20M</t>
   </si>
   <si>
@@ -276,15 +246,6 @@
     <t>02:00</t>
   </si>
   <si>
-    <t>02:01</t>
-  </si>
-  <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>06:48</t>
-  </si>
-  <si>
     <t>A1.csv</t>
   </si>
   <si>
@@ -303,9 +264,6 @@
     <t>14H.csv</t>
   </si>
   <si>
-    <t>14h.csv</t>
-  </si>
-  <si>
     <t>15H.csv</t>
   </si>
   <si>
@@ -324,9 +282,6 @@
     <t>20M.csv</t>
   </si>
   <si>
-    <t>4:01</t>
-  </si>
-  <si>
     <t>08:00</t>
   </si>
   <si>
@@ -366,19 +321,493 @@
     <t>12:00</t>
   </si>
   <si>
-    <t>A2</t>
-  </si>
-  <si>
-    <t>Alegria</t>
-  </si>
-  <si>
-    <t>Miedo</t>
-  </si>
-  <si>
-    <t>A2.csv</t>
-  </si>
-  <si>
     <t>06:50</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>02:16</t>
+  </si>
+  <si>
+    <t>02:31</t>
+  </si>
+  <si>
+    <t>02:32</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>03:06</t>
+  </si>
+  <si>
+    <t>03:50</t>
+  </si>
+  <si>
+    <t>03:57</t>
+  </si>
+  <si>
+    <t>03:58</t>
+  </si>
+  <si>
+    <t>4:10</t>
+  </si>
+  <si>
+    <t>04:13</t>
+  </si>
+  <si>
+    <t>04:14</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>07:01</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>07:42</t>
+  </si>
+  <si>
+    <t>07:43</t>
+  </si>
+  <si>
+    <t>08:49</t>
+  </si>
+  <si>
+    <t>3H</t>
+  </si>
+  <si>
+    <t>3H.csv</t>
+  </si>
+  <si>
+    <t>04:02</t>
+  </si>
+  <si>
+    <t>04:03</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>04:51</t>
+  </si>
+  <si>
+    <t>04:52</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>05:52</t>
+  </si>
+  <si>
+    <t>05:56</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>06:26</t>
+  </si>
+  <si>
+    <t>07:54</t>
+  </si>
+  <si>
+    <t>07:59</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>09:36</t>
+  </si>
+  <si>
+    <t>1M</t>
+  </si>
+  <si>
+    <t>1M.csv</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>0:00</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>5:25</t>
+  </si>
+  <si>
+    <t>5:26</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>06:31</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>08:31</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>04:40</t>
+  </si>
+  <si>
+    <t>04:45</t>
+  </si>
+  <si>
+    <t>06:06</t>
+  </si>
+  <si>
+    <t>01:37</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>01:46</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>02:45</t>
+  </si>
+  <si>
+    <t>02:46</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>04:06</t>
+  </si>
+  <si>
+    <t>04:34</t>
+  </si>
+  <si>
+    <t>04:39</t>
+  </si>
+  <si>
+    <t>05:22</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>05:26</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>01:25</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>01:31</t>
+  </si>
+  <si>
+    <t>01:40</t>
+  </si>
+  <si>
+    <t>04:44</t>
+  </si>
+  <si>
+    <t>04:48</t>
+  </si>
+  <si>
+    <t>01:55</t>
+  </si>
+  <si>
+    <t>01:56</t>
+  </si>
+  <si>
+    <t>04:49</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>01:49</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>04:21</t>
+  </si>
+  <si>
+    <t>05:10</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>10:56</t>
+  </si>
+  <si>
+    <t>14:18</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>14:26</t>
+  </si>
+  <si>
+    <t>16:06</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>16:11</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>12:14</t>
+  </si>
+  <si>
+    <t>12:16</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>3:35</t>
+  </si>
+  <si>
+    <t>03:30</t>
+  </si>
+  <si>
+    <t>01:36</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>02:11</t>
+  </si>
+  <si>
+    <t>04:30</t>
+  </si>
+  <si>
+    <t>04:24</t>
+  </si>
+  <si>
+    <t>04:31</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>05:36</t>
+  </si>
+  <si>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>08:32</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>08:33</t>
+  </si>
+  <si>
+    <t>09:16</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>10:46</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>11:31</t>
+  </si>
+  <si>
+    <t>12:07</t>
+  </si>
+  <si>
+    <t>12:12</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>13:49</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>14:06</t>
+  </si>
+  <si>
+    <t>15:08</t>
+  </si>
+  <si>
+    <t>15:13</t>
+  </si>
+  <si>
+    <t>15:14</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>16:08</t>
+  </si>
+  <si>
+    <t>16:09</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>17:31</t>
+  </si>
+  <si>
+    <t>18:09</t>
+  </si>
+  <si>
+    <t>18:16</t>
+  </si>
+  <si>
+    <t>18:17</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>19:21</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>20:32</t>
+  </si>
+  <si>
+    <t>20:33</t>
+  </si>
+  <si>
+    <t>21:01</t>
+  </si>
+  <si>
+    <t>21:06</t>
+  </si>
+  <si>
+    <t>21:07</t>
+  </si>
+  <si>
+    <t>21:33</t>
+  </si>
+  <si>
+    <t>21:38</t>
+  </si>
+  <si>
+    <t>03:08</t>
+  </si>
+  <si>
+    <t>03:09</t>
+  </si>
+  <si>
+    <t>02:06</t>
+  </si>
+  <si>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>03:31</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>07:34</t>
+  </si>
+  <si>
+    <t>07:39</t>
+  </si>
+  <si>
+    <t>08:03</t>
   </si>
 </sst>
 </file>
@@ -388,7 +817,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;$&quot;* #,##0.00_ ;_ &quot;$&quot;* \-#,##0.00_ ;_ &quot;$&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -413,14 +842,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -462,7 +883,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -472,10 +893,9 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -492,9 +912,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -532,9 +952,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -567,26 +987,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -619,26 +1022,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -812,18 +1198,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F94"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -843,724 +1229,1863 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>113</v>
-      </c>
-      <c r="B3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="5"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>87</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>108</v>
+        <v>54</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="F10" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>118</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>11</v>
+        <v>121</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>122</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>126</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>19</v>
+        <v>128</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>20</v>
+        <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>24</v>
+        <v>133</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>25</v>
+        <v>134</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>118</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>30</v>
-      </c>
       <c r="D17" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>33</v>
+        <v>254</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>34</v>
+        <v>87</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>36</v>
+        <v>73</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>37</v>
+        <v>255</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>38</v>
+        <v>198</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>7</v>
+        <v>256</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>151</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>41</v>
+        <v>172</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>257</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>73</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F24" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F24" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>54</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>9</v>
+      </c>
+      <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B32" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>17</v>
+      </c>
+      <c r="B33" t="s">
+        <v>75</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" t="s">
+        <v>76</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F35" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>26</v>
+      </c>
+      <c r="B36" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" t="s">
+        <v>76</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F41" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" t="s">
+        <v>79</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F42" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s">
+        <v>79</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="F43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>50</v>
+      </c>
+      <c r="B44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F44" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>50</v>
+      </c>
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F45" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>50</v>
+      </c>
+      <c r="B48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>50</v>
+      </c>
+      <c r="B49" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50" t="s">
+        <v>79</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="F52" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" t="s">
+        <v>79</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>50</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>50</v>
+      </c>
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>50</v>
+      </c>
+      <c r="B58" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>50</v>
+      </c>
+      <c r="B59" t="s">
+        <v>79</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>50</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>50</v>
+      </c>
+      <c r="B61" t="s">
+        <v>79</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>50</v>
+      </c>
+      <c r="B62" t="s">
+        <v>79</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>50</v>
+      </c>
+      <c r="B63" t="s">
+        <v>79</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>53</v>
+      </c>
+      <c r="B64" t="s">
+        <v>80</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>53</v>
+      </c>
+      <c r="B65" t="s">
+        <v>80</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>53</v>
+      </c>
+      <c r="B66" t="s">
+        <v>80</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>53</v>
+      </c>
+      <c r="B67" t="s">
+        <v>80</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>53</v>
+      </c>
+      <c r="B68" t="s">
+        <v>80</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>53</v>
+      </c>
+      <c r="B69" t="s">
+        <v>80</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>53</v>
+      </c>
+      <c r="B70" t="s">
+        <v>80</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>53</v>
+      </c>
+      <c r="B71" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>53</v>
+      </c>
+      <c r="B73" t="s">
+        <v>80</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="E73" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="B74" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" t="s">
+        <v>81</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="D75" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F75" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="D76" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="E29" s="2" t="s">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="D77" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" t="s">
-        <v>95</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30" s="2" t="s">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
         <v>67</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="B79" t="s">
+        <v>82</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>67</v>
+      </c>
+      <c r="B81" t="s">
+        <v>82</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>67</v>
+      </c>
+      <c r="B82" t="s">
+        <v>82</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>69</v>
+      </c>
+      <c r="B83" t="s">
+        <v>83</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>69</v>
+      </c>
+      <c r="B84" t="s">
+        <v>83</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F84" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" t="s">
-        <v>95</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="2" t="s">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
         <v>69</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="B85" t="s">
+        <v>83</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F85" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>69</v>
+      </c>
+      <c r="B86" t="s">
+        <v>83</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F86" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F87" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>69</v>
+      </c>
+      <c r="B88" t="s">
+        <v>83</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>69</v>
+      </c>
+      <c r="B89" t="s">
+        <v>83</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F89" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
         <v>70</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="B90" t="s">
+        <v>84</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>70</v>
+      </c>
+      <c r="B91" t="s">
+        <v>84</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F91" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F32" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" t="s">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" t="s">
+        <v>70</v>
+      </c>
+      <c r="B92" t="s">
+        <v>84</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93" t="s">
+        <v>84</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>70</v>
+      </c>
+      <c r="B94" t="s">
+        <v>84</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D94" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="E94" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" t="s">
-        <v>98</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>80</v>
-      </c>
-      <c r="B36" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" t="s">
-        <v>98</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F37" s="2" t="s">
+      <c r="F94" s="2" t="s">
         <v>10</v>
       </c>
     </row>
